--- a/模板-考勤.xlsx
+++ b/模板-考勤.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GZZ\kaoqin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CFE376-098B-496A-8158-4948951041FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC743D9-2B45-44C5-BBBD-F1674E2208C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -785,7 +785,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -872,9 +872,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -929,26 +926,26 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1273,7 +1270,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AU59"/>
+  <dimension ref="A1:AV59"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="44.15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="26" customWidth="1"/>
@@ -1309,153 +1306,155 @@
     <col min="38" max="38" width="10" style="29" customWidth="1"/>
     <col min="39" max="39" width="12.08203125" style="29" customWidth="1"/>
     <col min="40" max="40" width="10.9140625" style="29" customWidth="1"/>
-    <col min="41" max="44" width="10" style="29" customWidth="1"/>
-    <col min="45" max="45" width="26" style="27" customWidth="1"/>
-    <col min="46" max="16380" width="10" style="27" customWidth="1"/>
-    <col min="16381" max="16384" width="10" style="27"/>
+    <col min="41" max="45" width="10" style="29" customWidth="1"/>
+    <col min="46" max="46" width="26" style="27" customWidth="1"/>
+    <col min="47" max="16381" width="10" style="27" customWidth="1"/>
+    <col min="16382" max="16384" width="10" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:48" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53"/>
-      <c r="AA1" s="53"/>
-      <c r="AB1" s="53"/>
-      <c r="AC1" s="53"/>
-      <c r="AD1" s="53"/>
-      <c r="AE1" s="53"/>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="53"/>
-      <c r="AJ1" s="53"/>
-      <c r="AK1" s="53"/>
-      <c r="AL1" s="53"/>
-      <c r="AM1" s="53"/>
-      <c r="AN1" s="53"/>
-      <c r="AO1" s="53"/>
-      <c r="AP1" s="53"/>
-      <c r="AQ1" s="53"/>
-      <c r="AR1" s="53"/>
-      <c r="AS1" s="51"/>
-    </row>
-    <row r="2" spans="1:47" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="50"/>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="50"/>
+      <c r="AQ1" s="50"/>
+      <c r="AR1" s="50"/>
+      <c r="AS1" s="50"/>
+      <c r="AT1" s="48"/>
+    </row>
+    <row r="2" spans="1:48" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="49" t="s">
+      <c r="E2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="G2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="49" t="s">
+      <c r="I2" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="49" t="s">
+      <c r="J2" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="49" t="s">
+      <c r="K2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="49" t="s">
+      <c r="L2" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="49" t="s">
+      <c r="M2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="49" t="s">
+      <c r="N2" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="49"/>
-      <c r="U2" s="49"/>
-      <c r="V2" s="49"/>
-      <c r="W2" s="49"/>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="49"/>
-      <c r="AA2" s="49"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="49"/>
-      <c r="AE2" s="49"/>
-      <c r="AF2" s="49"/>
-      <c r="AG2" s="49"/>
-      <c r="AH2" s="49"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="49"/>
-      <c r="AK2" s="49"/>
-      <c r="AL2" s="49"/>
-      <c r="AM2" s="49"/>
-      <c r="AN2" s="49"/>
-      <c r="AO2" s="49"/>
-      <c r="AP2" s="49"/>
-      <c r="AQ2" s="49"/>
-      <c r="AR2" s="49"/>
-      <c r="AS2" s="49" t="s">
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+      <c r="AL2" s="51"/>
+      <c r="AM2" s="51"/>
+      <c r="AN2" s="51"/>
+      <c r="AO2" s="51"/>
+      <c r="AP2" s="51"/>
+      <c r="AQ2" s="51"/>
+      <c r="AR2" s="51"/>
+      <c r="AS2" s="51"/>
+      <c r="AT2" s="51" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
+    <row r="3" spans="1:48" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
       <c r="O3" s="7">
         <v>26</v>
       </c>
@@ -1543,28 +1542,29 @@
       <c r="AQ3" s="7">
         <v>24</v>
       </c>
-      <c r="AR3" s="7">
+      <c r="AR3" s="7"/>
+      <c r="AS3" s="7">
         <v>25</v>
       </c>
-      <c r="AS3" s="49"/>
-    </row>
-    <row r="4" spans="1:47" s="22" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="49"/>
+      <c r="AT3" s="51"/>
+    </row>
+    <row r="4" spans="1:48" s="22" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="51"/>
       <c r="B4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="49"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
       <c r="O4" s="7" t="s">
         <v>16</v>
       </c>
@@ -1652,12 +1652,13 @@
       <c r="AQ4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AR4" s="7" t="s">
+      <c r="AR4" s="7"/>
+      <c r="AS4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AS4" s="49"/>
-    </row>
-    <row r="5" spans="1:47" s="23" customFormat="1" ht="84.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AT4" s="51"/>
+    </row>
+    <row r="5" spans="1:48" s="23" customFormat="1" ht="84.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <f>ROW(A2)-1</f>
         <v>1</v>
@@ -1686,11 +1687,11 @@
       <c r="S5" s="9"/>
       <c r="T5" s="9"/>
       <c r="U5" s="9"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
       <c r="AA5" s="9"/>
       <c r="AB5" s="9"/>
       <c r="AC5" s="9"/>
@@ -1706,16 +1707,17 @@
       <c r="AM5" s="9"/>
       <c r="AN5" s="9"/>
       <c r="AO5" s="9"/>
-      <c r="AP5" s="46"/>
+      <c r="AP5" s="45"/>
       <c r="AQ5" s="9"/>
       <c r="AR5" s="9"/>
-      <c r="AS5" s="8" t="s">
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AT5" s="31"/>
-      <c r="AU5" s="31"/>
-    </row>
-    <row r="6" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU5" s="30"/>
+      <c r="AV5" s="30"/>
+    </row>
+    <row r="6" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <f t="shared" ref="A6:A41" si="0">ROW(A3)-1</f>
         <v>2</v>
@@ -1744,12 +1746,12 @@
       <c r="S6" s="9"/>
       <c r="T6" s="9"/>
       <c r="U6" s="9"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
       <c r="X6" s="9"/>
       <c r="Y6" s="9"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
       <c r="AB6" s="9"/>
       <c r="AC6" s="9"/>
       <c r="AD6" s="9"/>
@@ -1767,13 +1769,14 @@
       <c r="AP6" s="9"/>
       <c r="AQ6" s="9"/>
       <c r="AR6" s="9"/>
-      <c r="AS6" s="8" t="s">
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AT6" s="31"/>
-      <c r="AU6" s="31"/>
-    </row>
-    <row r="7" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU6" s="30"/>
+      <c r="AV6" s="30"/>
+    </row>
+    <row r="7" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1802,11 +1805,11 @@
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
       <c r="AB7" s="9"/>
       <c r="AC7" s="9"/>
@@ -1825,13 +1828,14 @@
       <c r="AP7" s="9"/>
       <c r="AQ7" s="9"/>
       <c r="AR7" s="9"/>
-      <c r="AS7" s="8" t="s">
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="AT7" s="31"/>
-      <c r="AU7" s="31"/>
-    </row>
-    <row r="8" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU7" s="30"/>
+      <c r="AV7" s="30"/>
+    </row>
+    <row r="8" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1880,21 +1884,22 @@
       <c r="AM8" s="9"/>
       <c r="AN8" s="9"/>
       <c r="AO8" s="9"/>
-      <c r="AP8" s="45"/>
+      <c r="AP8" s="44"/>
       <c r="AQ8" s="9"/>
       <c r="AR8" s="9"/>
-      <c r="AS8" s="8" t="s">
+      <c r="AS8" s="9"/>
+      <c r="AT8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="AT8" s="31"/>
-      <c r="AU8" s="31"/>
-    </row>
-    <row r="9" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU8" s="30"/>
+      <c r="AV8" s="30"/>
+    </row>
+    <row r="9" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="8"/>
@@ -1941,18 +1946,19 @@
       <c r="AP9" s="9"/>
       <c r="AQ9" s="9"/>
       <c r="AR9" s="9"/>
-      <c r="AS9" s="8" t="s">
+      <c r="AS9" s="9"/>
+      <c r="AT9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AT9" s="31"/>
-      <c r="AU9" s="31"/>
-    </row>
-    <row r="10" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU9" s="30"/>
+      <c r="AV9" s="30"/>
+    </row>
+    <row r="10" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="31" t="s">
         <v>33</v>
       </c>
       <c r="C10" s="8"/>
@@ -1999,18 +2005,19 @@
       <c r="AP10" s="9"/>
       <c r="AQ10" s="9"/>
       <c r="AR10" s="9"/>
-      <c r="AS10" s="8" t="s">
+      <c r="AS10" s="9"/>
+      <c r="AT10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AT10" s="31"/>
-      <c r="AU10" s="31"/>
-    </row>
-    <row r="11" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU10" s="30"/>
+      <c r="AV10" s="30"/>
+    </row>
+    <row r="11" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="31" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="8"/>
@@ -2057,18 +2064,19 @@
       <c r="AP11" s="9"/>
       <c r="AQ11" s="9"/>
       <c r="AR11" s="9"/>
-      <c r="AS11" s="9" t="s">
+      <c r="AS11" s="9"/>
+      <c r="AT11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="AT11" s="31"/>
-      <c r="AU11" s="31"/>
-    </row>
-    <row r="12" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU11" s="30"/>
+      <c r="AV11" s="30"/>
+    </row>
+    <row r="12" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="31" t="s">
         <v>37</v>
       </c>
       <c r="C12" s="8"/>
@@ -2092,7 +2100,7 @@
       <c r="S12" s="9"/>
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
-      <c r="V12" s="30"/>
+      <c r="V12" s="9"/>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
       <c r="Y12" s="9"/>
@@ -2110,23 +2118,24 @@
       <c r="AK12" s="9"/>
       <c r="AL12" s="9"/>
       <c r="AM12" s="9"/>
-      <c r="AN12" s="45"/>
+      <c r="AN12" s="44"/>
       <c r="AO12" s="9"/>
       <c r="AP12" s="9"/>
       <c r="AQ12" s="9"/>
       <c r="AR12" s="9"/>
-      <c r="AS12" s="9" t="s">
+      <c r="AS12" s="9"/>
+      <c r="AT12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AT12" s="31"/>
-      <c r="AU12" s="31"/>
-    </row>
-    <row r="13" spans="1:47" s="24" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU12" s="30"/>
+      <c r="AV12" s="30"/>
+    </row>
+    <row r="13" spans="1:48" s="24" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="32" t="s">
         <v>39</v>
       </c>
       <c r="C13" s="8"/>
@@ -2173,18 +2182,19 @@
       <c r="AP13" s="9"/>
       <c r="AQ13" s="9"/>
       <c r="AR13" s="9"/>
-      <c r="AS13" s="9" t="s">
+      <c r="AS13" s="9"/>
+      <c r="AT13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="AT13" s="31"/>
-      <c r="AU13" s="31"/>
-    </row>
-    <row r="14" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU13" s="30"/>
+      <c r="AV13" s="30"/>
+    </row>
+    <row r="14" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="31" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="8"/>
@@ -2231,13 +2241,14 @@
       <c r="AP14" s="9"/>
       <c r="AQ14" s="9"/>
       <c r="AR14" s="9"/>
-      <c r="AS14" s="9" t="s">
+      <c r="AS14" s="9"/>
+      <c r="AT14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="AT14" s="31"/>
-      <c r="AU14" s="31"/>
-    </row>
-    <row r="15" spans="1:47" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU14" s="30"/>
+      <c r="AV14" s="30"/>
+    </row>
+    <row r="15" spans="1:48" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2289,12 +2300,13 @@
       <c r="AP15" s="9"/>
       <c r="AQ15" s="9"/>
       <c r="AR15" s="9"/>
-      <c r="AS15" s="34" t="s">
+      <c r="AS15" s="9"/>
+      <c r="AT15" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="AT15" s="31"/>
-    </row>
-    <row r="16" spans="1:47" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU15" s="30"/>
+    </row>
+    <row r="16" spans="1:48" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2305,7 +2317,7 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
-      <c r="F16" s="32"/>
+      <c r="F16" s="31"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
@@ -2343,20 +2355,21 @@
       <c r="AM16" s="9"/>
       <c r="AN16" s="9"/>
       <c r="AO16" s="9"/>
-      <c r="AP16" s="45"/>
+      <c r="AP16" s="44"/>
       <c r="AQ16" s="9"/>
       <c r="AR16" s="9"/>
-      <c r="AS16" s="35" t="s">
+      <c r="AS16" s="9"/>
+      <c r="AT16" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="AT16" s="31"/>
-    </row>
-    <row r="17" spans="1:47" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU16" s="30"/>
+    </row>
+    <row r="17" spans="1:48" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="31" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="8"/>
@@ -2403,17 +2416,18 @@
       <c r="AP17" s="9"/>
       <c r="AQ17" s="9"/>
       <c r="AR17" s="9"/>
-      <c r="AS17" s="36" t="s">
+      <c r="AS17" s="9"/>
+      <c r="AT17" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="AT17" s="31"/>
-    </row>
-    <row r="18" spans="1:47" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU17" s="30"/>
+    </row>
+    <row r="18" spans="1:48" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="31" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="8"/>
@@ -2449,28 +2463,29 @@
       <c r="AE18" s="9"/>
       <c r="AF18" s="9"/>
       <c r="AG18" s="9"/>
-      <c r="AH18" s="37"/>
+      <c r="AH18" s="36"/>
       <c r="AI18" s="9"/>
       <c r="AJ18" s="9"/>
       <c r="AK18" s="9"/>
       <c r="AL18" s="9"/>
       <c r="AM18" s="9"/>
       <c r="AN18" s="9"/>
-      <c r="AO18" s="37"/>
+      <c r="AO18" s="36"/>
       <c r="AP18" s="9"/>
       <c r="AQ18" s="9"/>
       <c r="AR18" s="9"/>
-      <c r="AS18" s="9" t="s">
+      <c r="AS18" s="9"/>
+      <c r="AT18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="AT18" s="31"/>
-    </row>
-    <row r="19" spans="1:47" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU18" s="30"/>
+    </row>
+    <row r="19" spans="1:48" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="31" t="s">
         <v>50</v>
       </c>
       <c r="C19" s="8"/>
@@ -2517,17 +2532,18 @@
       <c r="AP19" s="9"/>
       <c r="AQ19" s="9"/>
       <c r="AR19" s="9"/>
-      <c r="AS19" s="9" t="s">
+      <c r="AS19" s="9"/>
+      <c r="AT19" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="AT19" s="31"/>
-    </row>
-    <row r="20" spans="1:47" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU19" s="30"/>
+    </row>
+    <row r="20" spans="1:48" s="23" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="31" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="8"/>
@@ -2563,7 +2579,7 @@
       <c r="AE20" s="9"/>
       <c r="AF20" s="9"/>
       <c r="AG20" s="9"/>
-      <c r="AH20" s="37"/>
+      <c r="AH20" s="36"/>
       <c r="AI20" s="9"/>
       <c r="AJ20" s="9"/>
       <c r="AK20" s="9"/>
@@ -2574,23 +2590,24 @@
       <c r="AP20" s="9"/>
       <c r="AQ20" s="9"/>
       <c r="AR20" s="9"/>
-      <c r="AS20" s="9" t="s">
+      <c r="AS20" s="9"/>
+      <c r="AT20" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="AT20" s="31"/>
-    </row>
-    <row r="21" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU20" s="30"/>
+    </row>
+    <row r="21" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="31" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
@@ -2631,17 +2648,18 @@
       <c r="AP21" s="9"/>
       <c r="AQ21" s="9"/>
       <c r="AR21" s="9"/>
-      <c r="AS21" s="36" t="s">
+      <c r="AS21" s="9"/>
+      <c r="AT21" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="AT21" s="31"/>
-    </row>
-    <row r="22" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU21" s="30"/>
+    </row>
+    <row r="22" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="31" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="8"/>
@@ -2688,18 +2706,19 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="9"/>
       <c r="AR22" s="9"/>
-      <c r="AS22" s="8" t="s">
+      <c r="AS22" s="9"/>
+      <c r="AT22" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="AT22" s="31"/>
-      <c r="AU22" s="31"/>
-    </row>
-    <row r="23" spans="1:47" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU22" s="30"/>
+      <c r="AV22" s="30"/>
+    </row>
+    <row r="23" spans="1:48" s="23" customFormat="1" ht="77" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="31" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="8"/>
@@ -2730,7 +2749,7 @@
       <c r="Z23" s="9"/>
       <c r="AA23" s="9"/>
       <c r="AB23" s="9"/>
-      <c r="AC23" s="45"/>
+      <c r="AC23" s="44"/>
       <c r="AD23" s="9"/>
       <c r="AE23" s="9"/>
       <c r="AF23" s="9"/>
@@ -2746,24 +2765,25 @@
       <c r="AP23" s="9"/>
       <c r="AQ23" s="9"/>
       <c r="AR23" s="9"/>
-      <c r="AS23" s="8" t="s">
+      <c r="AS23" s="9"/>
+      <c r="AT23" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="AT23" s="31"/>
-      <c r="AU23" s="31"/>
-    </row>
-    <row r="24" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU23" s="30"/>
+      <c r="AV23" s="30"/>
+    </row>
+    <row r="24" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="31" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="38"/>
+      <c r="F24" s="37"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
@@ -2804,17 +2824,18 @@
       <c r="AP24" s="9"/>
       <c r="AQ24" s="9"/>
       <c r="AR24" s="9"/>
-      <c r="AS24" s="9" t="s">
+      <c r="AS24" s="9"/>
+      <c r="AT24" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="AT24" s="31"/>
-    </row>
-    <row r="25" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU24" s="30"/>
+    </row>
+    <row r="25" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="31" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="8"/>
@@ -2855,23 +2876,24 @@
       <c r="AJ25" s="9"/>
       <c r="AK25" s="9"/>
       <c r="AL25" s="9"/>
-      <c r="AM25" s="45"/>
+      <c r="AM25" s="44"/>
       <c r="AN25" s="9"/>
       <c r="AO25" s="9"/>
       <c r="AP25" s="9"/>
       <c r="AQ25" s="9"/>
       <c r="AR25" s="9"/>
-      <c r="AS25" s="36" t="s">
+      <c r="AS25" s="9"/>
+      <c r="AT25" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="AT25" s="31"/>
-    </row>
-    <row r="26" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU25" s="30"/>
+    </row>
+    <row r="26" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="31" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="8"/>
@@ -2912,24 +2934,25 @@
       <c r="AJ26" s="9"/>
       <c r="AK26" s="9"/>
       <c r="AL26" s="9"/>
-      <c r="AM26" s="45"/>
+      <c r="AM26" s="44"/>
       <c r="AN26" s="9"/>
       <c r="AO26" s="9"/>
       <c r="AP26" s="9"/>
       <c r="AQ26" s="9"/>
       <c r="AR26" s="9"/>
-      <c r="AS26" s="9" t="s">
+      <c r="AS26" s="9"/>
+      <c r="AT26" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AT26" s="31"/>
-      <c r="AU26" s="31"/>
-    </row>
-    <row r="27" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU26" s="30"/>
+      <c r="AV26" s="30"/>
+    </row>
+    <row r="27" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="38" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="8"/>
@@ -2976,22 +2999,23 @@
       <c r="AP27" s="9"/>
       <c r="AQ27" s="9"/>
       <c r="AR27" s="9"/>
-      <c r="AS27" s="36" t="s">
+      <c r="AS27" s="9"/>
+      <c r="AT27" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="AT27" s="31"/>
-    </row>
-    <row r="28" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU27" s="30"/>
+    </row>
+    <row r="28" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="31" t="s">
         <v>67</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="38"/>
+      <c r="E28" s="37"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -3033,18 +3057,19 @@
       <c r="AP28" s="9"/>
       <c r="AQ28" s="9"/>
       <c r="AR28" s="9"/>
-      <c r="AS28" s="9" t="s">
+      <c r="AS28" s="9"/>
+      <c r="AT28" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AT28" s="31"/>
-      <c r="AU28" s="31"/>
-    </row>
-    <row r="29" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU28" s="30"/>
+      <c r="AV28" s="30"/>
+    </row>
+    <row r="29" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="31" t="s">
         <v>69</v>
       </c>
       <c r="C29" s="8"/>
@@ -3091,23 +3116,24 @@
       <c r="AP29" s="9"/>
       <c r="AQ29" s="9"/>
       <c r="AR29" s="9"/>
-      <c r="AS29" s="36" t="s">
+      <c r="AS29" s="9"/>
+      <c r="AT29" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="AT29" s="31"/>
-    </row>
-    <row r="30" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU29" s="30"/>
+    </row>
+    <row r="30" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="31" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="32"/>
+      <c r="F30" s="31"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
@@ -3148,23 +3174,24 @@
       <c r="AP30" s="9"/>
       <c r="AQ30" s="9"/>
       <c r="AR30" s="9"/>
-      <c r="AS30" s="8" t="s">
+      <c r="AS30" s="9"/>
+      <c r="AT30" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AT30" s="31"/>
-    </row>
-    <row r="31" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU30" s="30"/>
+    </row>
+    <row r="31" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="31" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
-      <c r="F31" s="32"/>
+      <c r="F31" s="31"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
@@ -3205,17 +3232,18 @@
       <c r="AP31" s="9"/>
       <c r="AQ31" s="9"/>
       <c r="AR31" s="9"/>
-      <c r="AS31" s="8" t="s">
+      <c r="AS31" s="9"/>
+      <c r="AT31" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="AT31" s="31"/>
-    </row>
-    <row r="32" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU31" s="30"/>
+    </row>
+    <row r="32" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="31" t="s">
         <v>75</v>
       </c>
       <c r="C32" s="8"/>
@@ -3237,7 +3265,7 @@
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
-      <c r="T32" s="45"/>
+      <c r="T32" s="44"/>
       <c r="U32" s="9"/>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
@@ -3262,13 +3290,14 @@
       <c r="AP32" s="9"/>
       <c r="AQ32" s="9"/>
       <c r="AR32" s="9"/>
-      <c r="AS32" s="9" t="s">
+      <c r="AS32" s="9"/>
+      <c r="AT32" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="AT32" s="31"/>
-      <c r="AU32" s="31"/>
-    </row>
-    <row r="33" spans="1:47" s="23" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU32" s="30"/>
+      <c r="AV32" s="30"/>
+    </row>
+    <row r="33" spans="1:48" s="23" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3320,23 +3349,24 @@
       <c r="AP33" s="9"/>
       <c r="AQ33" s="9"/>
       <c r="AR33" s="9"/>
-      <c r="AS33" s="9" t="s">
+      <c r="AS33" s="9"/>
+      <c r="AT33" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="AT33" s="31"/>
-    </row>
-    <row r="34" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU33" s="30"/>
+    </row>
+    <row r="34" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="31" t="s">
         <v>79</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
-      <c r="F34" s="32"/>
+      <c r="F34" s="31"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
@@ -3377,23 +3407,24 @@
       <c r="AP34" s="9"/>
       <c r="AQ34" s="9"/>
       <c r="AR34" s="9"/>
-      <c r="AS34" s="8" t="s">
+      <c r="AS34" s="9"/>
+      <c r="AT34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="AT34" s="31"/>
-    </row>
-    <row r="35" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU34" s="30"/>
+    </row>
+    <row r="35" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B35" s="32" t="s">
+      <c r="B35" s="31" t="s">
         <v>80</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="32"/>
+      <c r="F35" s="31"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
@@ -3434,17 +3465,18 @@
       <c r="AP35" s="9"/>
       <c r="AQ35" s="9"/>
       <c r="AR35" s="9"/>
-      <c r="AS35" s="8" t="s">
+      <c r="AS35" s="9"/>
+      <c r="AT35" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="AT35" s="31"/>
-    </row>
-    <row r="36" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU35" s="30"/>
+    </row>
+    <row r="36" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="31" t="s">
         <v>82</v>
       </c>
       <c r="C36" s="8"/>
@@ -3491,18 +3523,19 @@
       <c r="AP36" s="9"/>
       <c r="AQ36" s="9"/>
       <c r="AR36" s="9"/>
-      <c r="AS36" s="8" t="s">
+      <c r="AS36" s="9"/>
+      <c r="AT36" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="AT36" s="31"/>
-      <c r="AU36" s="31"/>
-    </row>
-    <row r="37" spans="1:47" s="25" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU36" s="30"/>
+      <c r="AV36" s="30"/>
+    </row>
+    <row r="37" spans="1:48" s="25" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B37" s="32" t="s">
+      <c r="B37" s="31" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="8"/>
@@ -3549,17 +3582,18 @@
       <c r="AP37" s="9"/>
       <c r="AQ37" s="9"/>
       <c r="AR37" s="9"/>
-      <c r="AS37" s="8" t="s">
+      <c r="AS37" s="9"/>
+      <c r="AT37" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="AT37" s="31"/>
-    </row>
-    <row r="38" spans="1:47" s="25" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU37" s="30"/>
+    </row>
+    <row r="38" spans="1:48" s="25" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B38" s="32" t="s">
+      <c r="B38" s="31" t="s">
         <v>86</v>
       </c>
       <c r="C38" s="8"/>
@@ -3606,17 +3640,18 @@
       <c r="AP38" s="9"/>
       <c r="AQ38" s="9"/>
       <c r="AR38" s="9"/>
-      <c r="AS38" s="9" t="s">
+      <c r="AS38" s="9"/>
+      <c r="AT38" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="AT38" s="31"/>
-    </row>
-    <row r="39" spans="1:47" s="25" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU38" s="30"/>
+    </row>
+    <row r="39" spans="1:48" s="25" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="31" t="s">
         <v>88</v>
       </c>
       <c r="C39" s="8"/>
@@ -3663,23 +3698,24 @@
       <c r="AP39" s="9"/>
       <c r="AQ39" s="9"/>
       <c r="AR39" s="9"/>
-      <c r="AS39" s="8" t="s">
+      <c r="AS39" s="9"/>
+      <c r="AT39" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="AT39" s="31"/>
-    </row>
-    <row r="40" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU39" s="30"/>
+    </row>
+    <row r="40" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B40" s="32" t="s">
+      <c r="B40" s="31" t="s">
         <v>90</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
-      <c r="F40" s="32"/>
+      <c r="F40" s="31"/>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
@@ -3720,23 +3756,24 @@
       <c r="AP40" s="9"/>
       <c r="AQ40" s="9"/>
       <c r="AR40" s="9"/>
-      <c r="AS40" s="8" t="s">
+      <c r="AS40" s="9"/>
+      <c r="AT40" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="AT40" s="31"/>
-    </row>
-    <row r="41" spans="1:47" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AU40" s="30"/>
+    </row>
+    <row r="41" spans="1:48" s="23" customFormat="1" ht="104" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="31" t="s">
         <v>92</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
-      <c r="F41" s="32"/>
+      <c r="F41" s="31"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
@@ -3777,61 +3814,62 @@
       <c r="AP41" s="9"/>
       <c r="AQ41" s="9"/>
       <c r="AR41" s="9"/>
-      <c r="AS41" s="8" t="s">
+      <c r="AS41" s="9"/>
+      <c r="AT41" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="AT41" s="31"/>
-    </row>
-    <row r="42" spans="1:47" s="25" customFormat="1" ht="70.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="54" t="s">
+      <c r="AU41" s="30"/>
+    </row>
+    <row r="42" spans="1:48" s="25" customFormat="1" ht="70.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="40">
+      <c r="B42" s="52"/>
+      <c r="C42" s="39">
         <f t="shared" ref="C42:N42" si="1">SUM(C5:C41)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="40">
+      <c r="D42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E42" s="40">
+      <c r="E42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F42" s="40">
+      <c r="F42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G42" s="40">
+      <c r="G42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H42" s="40">
+      <c r="H42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I42" s="40">
+      <c r="I42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J42" s="40">
+      <c r="J42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K42" s="40">
+      <c r="K42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L42" s="40">
+      <c r="L42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M42" s="40">
+      <c r="M42" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N42" s="40">
+      <c r="N42" s="39">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
@@ -3866,405 +3904,417 @@
       <c r="AQ42" s="9"/>
       <c r="AR42" s="9"/>
       <c r="AS42" s="9"/>
-      <c r="AT42" s="31"/>
-    </row>
-    <row r="43" spans="1:47" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="50" t="s">
+      <c r="AT42" s="9"/>
+      <c r="AU42" s="30"/>
+    </row>
+    <row r="43" spans="1:48" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="54" t="s">
         <v>147</v>
       </c>
-      <c r="B43" s="50"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="50"/>
-      <c r="Q43" s="50"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="50"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="50"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="50"/>
-      <c r="AA43" s="50"/>
-      <c r="AB43" s="50"/>
-      <c r="AC43" s="50"/>
-      <c r="AD43" s="50"/>
-      <c r="AE43" s="50"/>
-      <c r="AF43" s="50"/>
-      <c r="AG43" s="50"/>
-      <c r="AH43" s="50"/>
-      <c r="AI43" s="50"/>
-      <c r="AJ43" s="50"/>
-      <c r="AK43" s="50"/>
-      <c r="AL43" s="50"/>
-      <c r="AM43" s="50"/>
-      <c r="AN43" s="50"/>
-      <c r="AO43" s="50"/>
-      <c r="AP43" s="50"/>
-      <c r="AQ43" s="50"/>
-      <c r="AR43" s="50"/>
-      <c r="AS43" s="50"/>
-      <c r="AT43" s="31"/>
-    </row>
-    <row r="44" spans="1:47" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
-      <c r="B44" s="50"/>
-      <c r="C44" s="50"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="50"/>
-      <c r="P44" s="50"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50"/>
-      <c r="S44" s="50"/>
-      <c r="T44" s="50"/>
-      <c r="U44" s="50"/>
-      <c r="V44" s="50"/>
-      <c r="W44" s="50"/>
-      <c r="X44" s="50"/>
-      <c r="Y44" s="50"/>
-      <c r="Z44" s="50"/>
-      <c r="AA44" s="50"/>
-      <c r="AB44" s="50"/>
-      <c r="AC44" s="50"/>
-      <c r="AD44" s="50"/>
-      <c r="AE44" s="50"/>
-      <c r="AF44" s="50"/>
-      <c r="AG44" s="50"/>
-      <c r="AH44" s="50"/>
-      <c r="AI44" s="50"/>
-      <c r="AJ44" s="50"/>
-      <c r="AK44" s="50"/>
-      <c r="AL44" s="50"/>
-      <c r="AM44" s="50"/>
-      <c r="AN44" s="50"/>
-      <c r="AO44" s="50"/>
-      <c r="AP44" s="50"/>
-      <c r="AQ44" s="50"/>
-      <c r="AR44" s="50"/>
-      <c r="AS44" s="50"/>
-      <c r="AT44" s="31"/>
-    </row>
-    <row r="45" spans="1:47" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="41"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="41"/>
-      <c r="O45" s="43"/>
-      <c r="P45" s="43"/>
-      <c r="Q45" s="43"/>
-      <c r="R45" s="43"/>
-      <c r="S45" s="43"/>
-      <c r="T45" s="43"/>
-      <c r="U45" s="43"/>
-      <c r="V45" s="43"/>
-      <c r="W45" s="43"/>
-      <c r="X45" s="43"/>
-      <c r="Y45" s="43"/>
-      <c r="Z45" s="43"/>
-      <c r="AA45" s="43"/>
-      <c r="AB45" s="43"/>
-      <c r="AC45" s="43"/>
-      <c r="AD45" s="43"/>
-      <c r="AE45" s="43"/>
-      <c r="AF45" s="43"/>
-      <c r="AG45" s="43"/>
-      <c r="AH45" s="43"/>
-      <c r="AI45" s="43"/>
-      <c r="AJ45" s="43"/>
-      <c r="AK45" s="43"/>
-      <c r="AL45" s="43"/>
-      <c r="AM45" s="43"/>
-      <c r="AN45" s="43"/>
-      <c r="AO45" s="43"/>
-      <c r="AP45" s="43"/>
-      <c r="AQ45" s="43"/>
-      <c r="AR45" s="43"/>
-      <c r="AS45" s="41"/>
-      <c r="AT45" s="31"/>
-    </row>
-    <row r="53" spans="1:44" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="54"/>
+      <c r="J43" s="54"/>
+      <c r="K43" s="54"/>
+      <c r="L43" s="54"/>
+      <c r="M43" s="54"/>
+      <c r="N43" s="54"/>
+      <c r="O43" s="54"/>
+      <c r="P43" s="54"/>
+      <c r="Q43" s="54"/>
+      <c r="R43" s="54"/>
+      <c r="S43" s="54"/>
+      <c r="T43" s="54"/>
+      <c r="U43" s="54"/>
+      <c r="V43" s="54"/>
+      <c r="W43" s="54"/>
+      <c r="X43" s="54"/>
+      <c r="Y43" s="54"/>
+      <c r="Z43" s="54"/>
+      <c r="AA43" s="54"/>
+      <c r="AB43" s="54"/>
+      <c r="AC43" s="54"/>
+      <c r="AD43" s="54"/>
+      <c r="AE43" s="54"/>
+      <c r="AF43" s="54"/>
+      <c r="AG43" s="54"/>
+      <c r="AH43" s="54"/>
+      <c r="AI43" s="54"/>
+      <c r="AJ43" s="54"/>
+      <c r="AK43" s="54"/>
+      <c r="AL43" s="54"/>
+      <c r="AM43" s="54"/>
+      <c r="AN43" s="54"/>
+      <c r="AO43" s="54"/>
+      <c r="AP43" s="54"/>
+      <c r="AQ43" s="54"/>
+      <c r="AR43" s="54"/>
+      <c r="AS43" s="54"/>
+      <c r="AT43" s="54"/>
+      <c r="AU43" s="30"/>
+    </row>
+    <row r="44" spans="1:48" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="54"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="54"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="54"/>
+      <c r="L44" s="54"/>
+      <c r="M44" s="54"/>
+      <c r="N44" s="54"/>
+      <c r="O44" s="54"/>
+      <c r="P44" s="54"/>
+      <c r="Q44" s="54"/>
+      <c r="R44" s="54"/>
+      <c r="S44" s="54"/>
+      <c r="T44" s="54"/>
+      <c r="U44" s="54"/>
+      <c r="V44" s="54"/>
+      <c r="W44" s="54"/>
+      <c r="X44" s="54"/>
+      <c r="Y44" s="54"/>
+      <c r="Z44" s="54"/>
+      <c r="AA44" s="54"/>
+      <c r="AB44" s="54"/>
+      <c r="AC44" s="54"/>
+      <c r="AD44" s="54"/>
+      <c r="AE44" s="54"/>
+      <c r="AF44" s="54"/>
+      <c r="AG44" s="54"/>
+      <c r="AH44" s="54"/>
+      <c r="AI44" s="54"/>
+      <c r="AJ44" s="54"/>
+      <c r="AK44" s="54"/>
+      <c r="AL44" s="54"/>
+      <c r="AM44" s="54"/>
+      <c r="AN44" s="54"/>
+      <c r="AO44" s="54"/>
+      <c r="AP44" s="54"/>
+      <c r="AQ44" s="54"/>
+      <c r="AR44" s="54"/>
+      <c r="AS44" s="54"/>
+      <c r="AT44" s="54"/>
+      <c r="AU44" s="30"/>
+    </row>
+    <row r="45" spans="1:48" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="40"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="40"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="42"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="42"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="42"/>
+      <c r="T45" s="42"/>
+      <c r="U45" s="42"/>
+      <c r="V45" s="42"/>
+      <c r="W45" s="42"/>
+      <c r="X45" s="42"/>
+      <c r="Y45" s="42"/>
+      <c r="Z45" s="42"/>
+      <c r="AA45" s="42"/>
+      <c r="AB45" s="42"/>
+      <c r="AC45" s="42"/>
+      <c r="AD45" s="42"/>
+      <c r="AE45" s="42"/>
+      <c r="AF45" s="42"/>
+      <c r="AG45" s="42"/>
+      <c r="AH45" s="42"/>
+      <c r="AI45" s="42"/>
+      <c r="AJ45" s="42"/>
+      <c r="AK45" s="42"/>
+      <c r="AL45" s="42"/>
+      <c r="AM45" s="42"/>
+      <c r="AN45" s="42"/>
+      <c r="AO45" s="42"/>
+      <c r="AP45" s="42"/>
+      <c r="AQ45" s="42"/>
+      <c r="AR45" s="42"/>
+      <c r="AS45" s="42"/>
+      <c r="AT45" s="40"/>
+      <c r="AU45" s="30"/>
+    </row>
+    <row r="53" spans="1:45" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="26"/>
       <c r="C53" s="27"/>
       <c r="D53" s="28"/>
-      <c r="O53" s="44"/>
-      <c r="P53" s="44"/>
-      <c r="Q53" s="44"/>
-      <c r="R53" s="44"/>
-      <c r="S53" s="44"/>
-      <c r="T53" s="44"/>
-      <c r="U53" s="44"/>
-      <c r="V53" s="44"/>
-      <c r="W53" s="44"/>
-      <c r="X53" s="44"/>
-      <c r="Y53" s="44"/>
-      <c r="Z53" s="44"/>
-      <c r="AA53" s="44"/>
-      <c r="AB53" s="44"/>
-      <c r="AC53" s="44"/>
-      <c r="AD53" s="44"/>
-      <c r="AE53" s="44"/>
-      <c r="AF53" s="44"/>
-      <c r="AG53" s="44"/>
-      <c r="AH53" s="44"/>
-      <c r="AI53" s="44"/>
-      <c r="AJ53" s="44"/>
-      <c r="AK53" s="44"/>
-      <c r="AL53" s="44"/>
-      <c r="AM53" s="44"/>
-      <c r="AN53" s="44"/>
-      <c r="AO53" s="44"/>
-      <c r="AP53" s="44"/>
-      <c r="AQ53" s="44"/>
-      <c r="AR53" s="44"/>
-    </row>
-    <row r="54" spans="1:44" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O53" s="43"/>
+      <c r="P53" s="43"/>
+      <c r="Q53" s="43"/>
+      <c r="R53" s="43"/>
+      <c r="S53" s="43"/>
+      <c r="T53" s="43"/>
+      <c r="U53" s="43"/>
+      <c r="V53" s="43"/>
+      <c r="W53" s="43"/>
+      <c r="X53" s="43"/>
+      <c r="Y53" s="43"/>
+      <c r="Z53" s="43"/>
+      <c r="AA53" s="43"/>
+      <c r="AB53" s="43"/>
+      <c r="AC53" s="43"/>
+      <c r="AD53" s="43"/>
+      <c r="AE53" s="43"/>
+      <c r="AF53" s="43"/>
+      <c r="AG53" s="43"/>
+      <c r="AH53" s="43"/>
+      <c r="AI53" s="43"/>
+      <c r="AJ53" s="43"/>
+      <c r="AK53" s="43"/>
+      <c r="AL53" s="43"/>
+      <c r="AM53" s="43"/>
+      <c r="AN53" s="43"/>
+      <c r="AO53" s="43"/>
+      <c r="AP53" s="43"/>
+      <c r="AQ53" s="43"/>
+      <c r="AR53" s="43"/>
+      <c r="AS53" s="43"/>
+    </row>
+    <row r="54" spans="1:45" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="26"/>
       <c r="C54" s="27"/>
       <c r="D54" s="28"/>
-      <c r="O54" s="44"/>
-      <c r="P54" s="44"/>
-      <c r="Q54" s="44"/>
-      <c r="R54" s="44"/>
-      <c r="S54" s="44"/>
-      <c r="T54" s="44"/>
-      <c r="U54" s="44"/>
-      <c r="V54" s="44"/>
-      <c r="W54" s="44"/>
-      <c r="X54" s="44"/>
-      <c r="Y54" s="44"/>
-      <c r="Z54" s="44"/>
-      <c r="AA54" s="44"/>
-      <c r="AB54" s="44"/>
-      <c r="AC54" s="44"/>
-      <c r="AD54" s="44"/>
-      <c r="AE54" s="44"/>
-      <c r="AF54" s="44"/>
-      <c r="AG54" s="44"/>
-      <c r="AH54" s="44"/>
-      <c r="AI54" s="44"/>
-      <c r="AJ54" s="44"/>
-      <c r="AK54" s="44"/>
-      <c r="AL54" s="44"/>
-      <c r="AM54" s="44"/>
-      <c r="AN54" s="44"/>
-      <c r="AO54" s="44"/>
-      <c r="AP54" s="44"/>
-      <c r="AQ54" s="44"/>
-      <c r="AR54" s="44"/>
-    </row>
-    <row r="55" spans="1:44" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O54" s="43"/>
+      <c r="P54" s="43"/>
+      <c r="Q54" s="43"/>
+      <c r="R54" s="43"/>
+      <c r="S54" s="43"/>
+      <c r="T54" s="43"/>
+      <c r="U54" s="43"/>
+      <c r="V54" s="43"/>
+      <c r="W54" s="43"/>
+      <c r="X54" s="43"/>
+      <c r="Y54" s="43"/>
+      <c r="Z54" s="43"/>
+      <c r="AA54" s="43"/>
+      <c r="AB54" s="43"/>
+      <c r="AC54" s="43"/>
+      <c r="AD54" s="43"/>
+      <c r="AE54" s="43"/>
+      <c r="AF54" s="43"/>
+      <c r="AG54" s="43"/>
+      <c r="AH54" s="43"/>
+      <c r="AI54" s="43"/>
+      <c r="AJ54" s="43"/>
+      <c r="AK54" s="43"/>
+      <c r="AL54" s="43"/>
+      <c r="AM54" s="43"/>
+      <c r="AN54" s="43"/>
+      <c r="AO54" s="43"/>
+      <c r="AP54" s="43"/>
+      <c r="AQ54" s="43"/>
+      <c r="AR54" s="43"/>
+      <c r="AS54" s="43"/>
+    </row>
+    <row r="55" spans="1:45" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="26"/>
       <c r="C55" s="27"/>
       <c r="D55" s="28"/>
-      <c r="O55" s="44"/>
-      <c r="P55" s="44"/>
-      <c r="Q55" s="44"/>
-      <c r="R55" s="44"/>
-      <c r="S55" s="44"/>
-      <c r="T55" s="44"/>
-      <c r="U55" s="44"/>
-      <c r="V55" s="44"/>
-      <c r="W55" s="44"/>
-      <c r="X55" s="44"/>
-      <c r="Y55" s="44"/>
-      <c r="Z55" s="44"/>
-      <c r="AA55" s="44"/>
-      <c r="AB55" s="44"/>
-      <c r="AC55" s="44"/>
-      <c r="AD55" s="44"/>
-      <c r="AE55" s="44"/>
-      <c r="AF55" s="44"/>
-      <c r="AG55" s="44"/>
-      <c r="AH55" s="44"/>
-      <c r="AI55" s="44"/>
-      <c r="AJ55" s="44"/>
-      <c r="AK55" s="44"/>
-      <c r="AL55" s="44"/>
-      <c r="AM55" s="44"/>
-      <c r="AN55" s="44"/>
-      <c r="AO55" s="44"/>
-      <c r="AP55" s="44"/>
-      <c r="AQ55" s="44"/>
-      <c r="AR55" s="44"/>
-    </row>
-    <row r="56" spans="1:44" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O55" s="43"/>
+      <c r="P55" s="43"/>
+      <c r="Q55" s="43"/>
+      <c r="R55" s="43"/>
+      <c r="S55" s="43"/>
+      <c r="T55" s="43"/>
+      <c r="U55" s="43"/>
+      <c r="V55" s="43"/>
+      <c r="W55" s="43"/>
+      <c r="X55" s="43"/>
+      <c r="Y55" s="43"/>
+      <c r="Z55" s="43"/>
+      <c r="AA55" s="43"/>
+      <c r="AB55" s="43"/>
+      <c r="AC55" s="43"/>
+      <c r="AD55" s="43"/>
+      <c r="AE55" s="43"/>
+      <c r="AF55" s="43"/>
+      <c r="AG55" s="43"/>
+      <c r="AH55" s="43"/>
+      <c r="AI55" s="43"/>
+      <c r="AJ55" s="43"/>
+      <c r="AK55" s="43"/>
+      <c r="AL55" s="43"/>
+      <c r="AM55" s="43"/>
+      <c r="AN55" s="43"/>
+      <c r="AO55" s="43"/>
+      <c r="AP55" s="43"/>
+      <c r="AQ55" s="43"/>
+      <c r="AR55" s="43"/>
+      <c r="AS55" s="43"/>
+    </row>
+    <row r="56" spans="1:45" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26"/>
       <c r="C56" s="27"/>
       <c r="D56" s="28"/>
-      <c r="O56" s="44"/>
-      <c r="P56" s="44"/>
-      <c r="Q56" s="44"/>
-      <c r="R56" s="44"/>
-      <c r="S56" s="44"/>
-      <c r="T56" s="44"/>
-      <c r="U56" s="44"/>
-      <c r="V56" s="44"/>
-      <c r="W56" s="44"/>
-      <c r="X56" s="44"/>
-      <c r="Y56" s="44"/>
-      <c r="Z56" s="44"/>
-      <c r="AA56" s="44"/>
-      <c r="AB56" s="44"/>
-      <c r="AC56" s="44"/>
-      <c r="AD56" s="44"/>
-      <c r="AE56" s="44"/>
-      <c r="AF56" s="44"/>
-      <c r="AG56" s="44"/>
-      <c r="AH56" s="44"/>
-      <c r="AI56" s="44"/>
-      <c r="AJ56" s="44"/>
-      <c r="AK56" s="44"/>
-      <c r="AL56" s="44"/>
-      <c r="AM56" s="44"/>
-      <c r="AN56" s="44"/>
-      <c r="AO56" s="44"/>
-      <c r="AP56" s="44"/>
-      <c r="AQ56" s="44"/>
-      <c r="AR56" s="44"/>
-    </row>
-    <row r="57" spans="1:44" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O56" s="43"/>
+      <c r="P56" s="43"/>
+      <c r="Q56" s="43"/>
+      <c r="R56" s="43"/>
+      <c r="S56" s="43"/>
+      <c r="T56" s="43"/>
+      <c r="U56" s="43"/>
+      <c r="V56" s="43"/>
+      <c r="W56" s="43"/>
+      <c r="X56" s="43"/>
+      <c r="Y56" s="43"/>
+      <c r="Z56" s="43"/>
+      <c r="AA56" s="43"/>
+      <c r="AB56" s="43"/>
+      <c r="AC56" s="43"/>
+      <c r="AD56" s="43"/>
+      <c r="AE56" s="43"/>
+      <c r="AF56" s="43"/>
+      <c r="AG56" s="43"/>
+      <c r="AH56" s="43"/>
+      <c r="AI56" s="43"/>
+      <c r="AJ56" s="43"/>
+      <c r="AK56" s="43"/>
+      <c r="AL56" s="43"/>
+      <c r="AM56" s="43"/>
+      <c r="AN56" s="43"/>
+      <c r="AO56" s="43"/>
+      <c r="AP56" s="43"/>
+      <c r="AQ56" s="43"/>
+      <c r="AR56" s="43"/>
+      <c r="AS56" s="43"/>
+    </row>
+    <row r="57" spans="1:45" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26"/>
       <c r="C57" s="27"/>
       <c r="D57" s="28"/>
-      <c r="O57" s="44"/>
-      <c r="P57" s="44"/>
-      <c r="Q57" s="44"/>
-      <c r="R57" s="44"/>
-      <c r="S57" s="44"/>
-      <c r="T57" s="44"/>
-      <c r="U57" s="44"/>
-      <c r="V57" s="44"/>
-      <c r="W57" s="44"/>
-      <c r="X57" s="44"/>
-      <c r="Y57" s="44"/>
-      <c r="Z57" s="44"/>
-      <c r="AA57" s="44"/>
-      <c r="AB57" s="44"/>
-      <c r="AC57" s="44"/>
-      <c r="AD57" s="44"/>
-      <c r="AE57" s="44"/>
-      <c r="AF57" s="44"/>
-      <c r="AG57" s="44"/>
-      <c r="AH57" s="44"/>
-      <c r="AI57" s="44"/>
-      <c r="AJ57" s="44"/>
-      <c r="AK57" s="44"/>
-      <c r="AL57" s="44"/>
-      <c r="AM57" s="44"/>
-      <c r="AN57" s="44"/>
-      <c r="AO57" s="44"/>
-      <c r="AP57" s="44"/>
-      <c r="AQ57" s="44"/>
-      <c r="AR57" s="44"/>
-    </row>
-    <row r="58" spans="1:44" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O57" s="43"/>
+      <c r="P57" s="43"/>
+      <c r="Q57" s="43"/>
+      <c r="R57" s="43"/>
+      <c r="S57" s="43"/>
+      <c r="T57" s="43"/>
+      <c r="U57" s="43"/>
+      <c r="V57" s="43"/>
+      <c r="W57" s="43"/>
+      <c r="X57" s="43"/>
+      <c r="Y57" s="43"/>
+      <c r="Z57" s="43"/>
+      <c r="AA57" s="43"/>
+      <c r="AB57" s="43"/>
+      <c r="AC57" s="43"/>
+      <c r="AD57" s="43"/>
+      <c r="AE57" s="43"/>
+      <c r="AF57" s="43"/>
+      <c r="AG57" s="43"/>
+      <c r="AH57" s="43"/>
+      <c r="AI57" s="43"/>
+      <c r="AJ57" s="43"/>
+      <c r="AK57" s="43"/>
+      <c r="AL57" s="43"/>
+      <c r="AM57" s="43"/>
+      <c r="AN57" s="43"/>
+      <c r="AO57" s="43"/>
+      <c r="AP57" s="43"/>
+      <c r="AQ57" s="43"/>
+      <c r="AR57" s="43"/>
+      <c r="AS57" s="43"/>
+    </row>
+    <row r="58" spans="1:45" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26"/>
       <c r="C58" s="27"/>
       <c r="D58" s="28"/>
-      <c r="O58" s="44"/>
-      <c r="P58" s="44"/>
-      <c r="Q58" s="44"/>
-      <c r="R58" s="44"/>
-      <c r="S58" s="44"/>
-      <c r="T58" s="44"/>
-      <c r="U58" s="44"/>
-      <c r="V58" s="44"/>
-      <c r="W58" s="44"/>
-      <c r="X58" s="44"/>
-      <c r="Y58" s="44"/>
-      <c r="Z58" s="44"/>
-      <c r="AA58" s="44"/>
-      <c r="AB58" s="44"/>
-      <c r="AC58" s="44"/>
-      <c r="AD58" s="44"/>
-      <c r="AE58" s="44"/>
-      <c r="AF58" s="44"/>
-      <c r="AG58" s="44"/>
-      <c r="AH58" s="44"/>
-      <c r="AI58" s="44"/>
-      <c r="AJ58" s="44"/>
-      <c r="AK58" s="44"/>
-      <c r="AL58" s="44"/>
-      <c r="AM58" s="44"/>
-      <c r="AN58" s="44"/>
-      <c r="AO58" s="44"/>
-      <c r="AP58" s="44"/>
-      <c r="AQ58" s="44"/>
-      <c r="AR58" s="44"/>
-    </row>
-    <row r="59" spans="1:44" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O58" s="43"/>
+      <c r="P58" s="43"/>
+      <c r="Q58" s="43"/>
+      <c r="R58" s="43"/>
+      <c r="S58" s="43"/>
+      <c r="T58" s="43"/>
+      <c r="U58" s="43"/>
+      <c r="V58" s="43"/>
+      <c r="W58" s="43"/>
+      <c r="X58" s="43"/>
+      <c r="Y58" s="43"/>
+      <c r="Z58" s="43"/>
+      <c r="AA58" s="43"/>
+      <c r="AB58" s="43"/>
+      <c r="AC58" s="43"/>
+      <c r="AD58" s="43"/>
+      <c r="AE58" s="43"/>
+      <c r="AF58" s="43"/>
+      <c r="AG58" s="43"/>
+      <c r="AH58" s="43"/>
+      <c r="AI58" s="43"/>
+      <c r="AJ58" s="43"/>
+      <c r="AK58" s="43"/>
+      <c r="AL58" s="43"/>
+      <c r="AM58" s="43"/>
+      <c r="AN58" s="43"/>
+      <c r="AO58" s="43"/>
+      <c r="AP58" s="43"/>
+      <c r="AQ58" s="43"/>
+      <c r="AR58" s="43"/>
+      <c r="AS58" s="43"/>
+    </row>
+    <row r="59" spans="1:45" s="25" customFormat="1" ht="44.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26"/>
       <c r="C59" s="27"/>
       <c r="D59" s="28"/>
-      <c r="O59" s="44"/>
-      <c r="P59" s="44"/>
-      <c r="Q59" s="44"/>
-      <c r="R59" s="44"/>
-      <c r="S59" s="44"/>
-      <c r="T59" s="44"/>
-      <c r="U59" s="44"/>
-      <c r="V59" s="44"/>
-      <c r="W59" s="44"/>
-      <c r="X59" s="44"/>
-      <c r="Y59" s="44"/>
-      <c r="Z59" s="44"/>
-      <c r="AA59" s="44"/>
-      <c r="AB59" s="44"/>
-      <c r="AC59" s="44"/>
-      <c r="AD59" s="44"/>
-      <c r="AE59" s="44"/>
-      <c r="AF59" s="44"/>
-      <c r="AG59" s="44"/>
-      <c r="AH59" s="44"/>
-      <c r="AI59" s="44"/>
-      <c r="AJ59" s="44"/>
-      <c r="AK59" s="44"/>
-      <c r="AL59" s="44"/>
-      <c r="AM59" s="44"/>
-      <c r="AN59" s="44"/>
-      <c r="AO59" s="44"/>
-      <c r="AP59" s="44"/>
-      <c r="AQ59" s="44"/>
-      <c r="AR59" s="44"/>
+      <c r="O59" s="43"/>
+      <c r="P59" s="43"/>
+      <c r="Q59" s="43"/>
+      <c r="R59" s="43"/>
+      <c r="S59" s="43"/>
+      <c r="T59" s="43"/>
+      <c r="U59" s="43"/>
+      <c r="V59" s="43"/>
+      <c r="W59" s="43"/>
+      <c r="X59" s="43"/>
+      <c r="Y59" s="43"/>
+      <c r="Z59" s="43"/>
+      <c r="AA59" s="43"/>
+      <c r="AB59" s="43"/>
+      <c r="AC59" s="43"/>
+      <c r="AD59" s="43"/>
+      <c r="AE59" s="43"/>
+      <c r="AF59" s="43"/>
+      <c r="AG59" s="43"/>
+      <c r="AH59" s="43"/>
+      <c r="AI59" s="43"/>
+      <c r="AJ59" s="43"/>
+      <c r="AK59" s="43"/>
+      <c r="AL59" s="43"/>
+      <c r="AM59" s="43"/>
+      <c r="AN59" s="43"/>
+      <c r="AO59" s="43"/>
+      <c r="AP59" s="43"/>
+      <c r="AQ59" s="43"/>
+      <c r="AR59" s="43"/>
+      <c r="AS59" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="AS2:AS4"/>
-    <mergeCell ref="A43:AS44"/>
-    <mergeCell ref="A1:AS1"/>
-    <mergeCell ref="O2:AR2"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="AT2:AT4"/>
+    <mergeCell ref="A43:AT44"/>
+    <mergeCell ref="A1:AT1"/>
+    <mergeCell ref="O2:AS2"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B3"/>
@@ -4279,7 +4329,6 @@
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="L2:L4"/>
     <mergeCell ref="M2:M4"/>
-    <mergeCell ref="N2:N4"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.98402777777777795" right="0.196527777777778" top="0.31458333333333299" bottom="0.156944444444444" header="0.39305555555555599" footer="0.27500000000000002"/>
@@ -4303,12 +4352,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" spans="1:4" ht="23.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
@@ -4602,7 +4651,7 @@
       <c r="B21" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="47" t="s">
         <v>145</v>
       </c>
       <c r="D21" s="14">
@@ -4632,7 +4681,7 @@
       <c r="B23" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="47" t="s">
         <v>144</v>
       </c>
       <c r="D23" s="14">
@@ -4872,7 +4921,7 @@
       <c r="B39" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="47" t="s">
+      <c r="C39" s="46" t="s">
         <v>143</v>
       </c>
       <c r="D39" s="20">
@@ -4905,143 +4954,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="51"/>
-      <c r="AD1" s="51"/>
-      <c r="AE1" s="51"/>
-      <c r="AF1" s="51"/>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
+      <c r="AD1" s="48"/>
+      <c r="AE1" s="48"/>
+      <c r="AF1" s="48"/>
+      <c r="AG1" s="48"/>
+      <c r="AH1" s="48"/>
+      <c r="AI1" s="48"/>
+      <c r="AJ1" s="48"/>
+      <c r="AK1" s="48"/>
+      <c r="AL1" s="48"/>
+      <c r="AM1" s="48"/>
+      <c r="AN1" s="48"/>
+      <c r="AO1" s="48"/>
+      <c r="AP1" s="48"/>
+      <c r="AQ1" s="48"/>
+      <c r="AR1" s="48"/>
+      <c r="AS1" s="48"/>
     </row>
     <row r="2" spans="1:46" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="57" t="s">
+      <c r="J2" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="57" t="s">
+      <c r="L2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="57" t="s">
+      <c r="M2" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="57"/>
-      <c r="Z2" s="57"/>
-      <c r="AA2" s="57"/>
-      <c r="AB2" s="57"/>
-      <c r="AC2" s="57"/>
-      <c r="AD2" s="57"/>
-      <c r="AE2" s="57"/>
-      <c r="AF2" s="57"/>
-      <c r="AG2" s="57"/>
-      <c r="AH2" s="57"/>
-      <c r="AI2" s="57"/>
-      <c r="AJ2" s="57"/>
-      <c r="AK2" s="57"/>
-      <c r="AL2" s="57"/>
-      <c r="AM2" s="57"/>
-      <c r="AN2" s="57"/>
-      <c r="AO2" s="57"/>
-      <c r="AP2" s="57"/>
-      <c r="AQ2" s="57"/>
-      <c r="AR2" s="57"/>
-      <c r="AS2" s="57" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="56"/>
+      <c r="AC2" s="56"/>
+      <c r="AD2" s="56"/>
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="56"/>
+      <c r="AP2" s="56"/>
+      <c r="AQ2" s="56"/>
+      <c r="AR2" s="56"/>
+      <c r="AS2" s="56" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:46" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
       <c r="N3" s="7">
         <v>26</v>
       </c>
@@ -5135,24 +5184,24 @@
       <c r="AR3" s="7">
         <v>25</v>
       </c>
-      <c r="AS3" s="57"/>
+      <c r="AS3" s="56"/>
     </row>
     <row r="4" spans="1:46" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="57"/>
+      <c r="A4" s="56"/>
       <c r="B4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
       <c r="N4" s="7" t="s">
         <v>16</v>
       </c>
@@ -5246,7 +5295,7 @@
       <c r="AR4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AS4" s="57"/>
+      <c r="AS4" s="56"/>
     </row>
     <row r="5" spans="1:46" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
@@ -5661,10 +5710,10 @@
       <c r="AT7" s="11"/>
     </row>
     <row r="8" spans="1:46" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="54"/>
+      <c r="B8" s="52"/>
       <c r="C8" s="8">
         <f>SUM(C5:C7)</f>
         <v>93</v>
@@ -5743,104 +5792,103 @@
       <c r="AS8" s="8"/>
     </row>
     <row r="9" spans="1:46" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="59"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="59"/>
-      <c r="M9" s="59"/>
-      <c r="N9" s="59"/>
-      <c r="O9" s="59"/>
-      <c r="P9" s="59"/>
-      <c r="Q9" s="59"/>
-      <c r="R9" s="59"/>
-      <c r="S9" s="59"/>
-      <c r="T9" s="59"/>
-      <c r="U9" s="59"/>
-      <c r="V9" s="59"/>
-      <c r="W9" s="59"/>
-      <c r="X9" s="59"/>
-      <c r="Y9" s="59"/>
-      <c r="Z9" s="59"/>
-      <c r="AA9" s="59"/>
-      <c r="AB9" s="59"/>
-      <c r="AC9" s="59"/>
-      <c r="AD9" s="59"/>
-      <c r="AE9" s="59"/>
-      <c r="AF9" s="59"/>
-      <c r="AG9" s="59"/>
-      <c r="AH9" s="59"/>
-      <c r="AI9" s="59"/>
-      <c r="AJ9" s="59"/>
-      <c r="AK9" s="59"/>
-      <c r="AL9" s="59"/>
-      <c r="AM9" s="59"/>
-      <c r="AN9" s="59"/>
-      <c r="AO9" s="59"/>
-      <c r="AP9" s="59"/>
-      <c r="AQ9" s="59"/>
-      <c r="AR9" s="59"/>
-      <c r="AS9" s="60"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
+      <c r="S9" s="58"/>
+      <c r="T9" s="58"/>
+      <c r="U9" s="58"/>
+      <c r="V9" s="58"/>
+      <c r="W9" s="58"/>
+      <c r="X9" s="58"/>
+      <c r="Y9" s="58"/>
+      <c r="Z9" s="58"/>
+      <c r="AA9" s="58"/>
+      <c r="AB9" s="58"/>
+      <c r="AC9" s="58"/>
+      <c r="AD9" s="58"/>
+      <c r="AE9" s="58"/>
+      <c r="AF9" s="58"/>
+      <c r="AG9" s="58"/>
+      <c r="AH9" s="58"/>
+      <c r="AI9" s="58"/>
+      <c r="AJ9" s="58"/>
+      <c r="AK9" s="58"/>
+      <c r="AL9" s="58"/>
+      <c r="AM9" s="58"/>
+      <c r="AN9" s="58"/>
+      <c r="AO9" s="58"/>
+      <c r="AP9" s="58"/>
+      <c r="AQ9" s="58"/>
+      <c r="AR9" s="58"/>
+      <c r="AS9" s="59"/>
     </row>
     <row r="10" spans="1:46" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="61"/>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="62"/>
-      <c r="M10" s="62"/>
-      <c r="N10" s="62"/>
-      <c r="O10" s="62"/>
-      <c r="P10" s="62"/>
-      <c r="Q10" s="62"/>
-      <c r="R10" s="62"/>
-      <c r="S10" s="62"/>
-      <c r="T10" s="62"/>
-      <c r="U10" s="62"/>
-      <c r="V10" s="62"/>
-      <c r="W10" s="62"/>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="62"/>
-      <c r="Z10" s="62"/>
-      <c r="AA10" s="62"/>
-      <c r="AB10" s="62"/>
-      <c r="AC10" s="62"/>
-      <c r="AD10" s="62"/>
-      <c r="AE10" s="62"/>
-      <c r="AF10" s="62"/>
-      <c r="AG10" s="62"/>
-      <c r="AH10" s="62"/>
-      <c r="AI10" s="62"/>
-      <c r="AJ10" s="62"/>
-      <c r="AK10" s="62"/>
-      <c r="AL10" s="62"/>
-      <c r="AM10" s="62"/>
-      <c r="AN10" s="62"/>
-      <c r="AO10" s="62"/>
-      <c r="AP10" s="62"/>
-      <c r="AQ10" s="62"/>
-      <c r="AR10" s="62"/>
-      <c r="AS10" s="63"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="61"/>
+      <c r="T10" s="61"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="61"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="61"/>
+      <c r="Y10" s="61"/>
+      <c r="Z10" s="61"/>
+      <c r="AA10" s="61"/>
+      <c r="AB10" s="61"/>
+      <c r="AC10" s="61"/>
+      <c r="AD10" s="61"/>
+      <c r="AE10" s="61"/>
+      <c r="AF10" s="61"/>
+      <c r="AG10" s="61"/>
+      <c r="AH10" s="61"/>
+      <c r="AI10" s="61"/>
+      <c r="AJ10" s="61"/>
+      <c r="AK10" s="61"/>
+      <c r="AL10" s="61"/>
+      <c r="AM10" s="61"/>
+      <c r="AN10" s="61"/>
+      <c r="AO10" s="61"/>
+      <c r="AP10" s="61"/>
+      <c r="AQ10" s="61"/>
+      <c r="AR10" s="61"/>
+      <c r="AS10" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="K2:K4"/>
     <mergeCell ref="L2:L4"/>
     <mergeCell ref="M2:M4"/>
     <mergeCell ref="AS2:AS4"/>
@@ -5858,6 +5906,7 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.156944444444444" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
@@ -5882,12 +5931,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="64"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="63"/>
     </row>
     <row r="2" spans="1:4" ht="29.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
